--- a/data/trans_dic/P45C_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,48; 10,81</t>
+          <t>7,39; 10,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 13,52</t>
+          <t>9,5; 13,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 8,47</t>
+          <t>4,89; 8,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,14; 18,2</t>
+          <t>12,56; 18,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 8,2</t>
+          <t>5,44; 8,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,3</t>
+          <t>8,07; 11,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,12</t>
+          <t>4,94; 8,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,62; 10,96</t>
+          <t>7,72; 10,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 8,85</t>
+          <t>6,68; 8,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,0; 11,53</t>
+          <t>9,12; 11,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 7,74</t>
+          <t>5,29; 7,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,17; 13,25</t>
+          <t>10,11; 13,26</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 20,92</t>
+          <t>17,09; 20,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,99; 21,65</t>
+          <t>17,88; 21,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,81; 17,38</t>
+          <t>13,78; 17,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,38; 18,78</t>
+          <t>11,3; 18,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,65; 17,31</t>
+          <t>13,47; 17,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,17; 17,85</t>
+          <t>14,18; 17,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,31; 17,64</t>
+          <t>14,29; 17,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 15,17</t>
+          <t>9,39; 15,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,87; 18,43</t>
+          <t>15,8; 18,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,65; 19,24</t>
+          <t>16,63; 19,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 16,85</t>
+          <t>14,59; 16,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,41; 16,43</t>
+          <t>11,71; 16,48</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,72; 21,49</t>
+          <t>14,93; 21,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,6; 26,31</t>
+          <t>18,49; 26,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,32; 19,4</t>
+          <t>12,57; 19,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,4; 17,13</t>
+          <t>11,19; 16,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,03; 22,18</t>
+          <t>15,52; 22,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,04; 19,06</t>
+          <t>12,03; 19,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,79; 21,69</t>
+          <t>14,78; 21,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,2; 16,52</t>
+          <t>11,4; 16,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,08; 21,15</t>
+          <t>16,04; 20,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,11; 21,57</t>
+          <t>16,3; 21,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,57; 19,42</t>
+          <t>14,9; 19,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,9; 15,75</t>
+          <t>11,96; 15,95</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,4; 16,93</t>
+          <t>14,42; 17,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,36; 19,04</t>
+          <t>16,36; 18,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,37; 14,77</t>
+          <t>12,42; 14,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 17,25</t>
+          <t>11,93; 17,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 13,53</t>
+          <t>11,4; 13,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,3; 14,71</t>
+          <t>12,13; 14,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,38; 14,74</t>
+          <t>12,36; 14,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,12; 13,58</t>
+          <t>10,09; 13,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,16; 14,92</t>
+          <t>13,15; 14,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,76; 16,5</t>
+          <t>14,58; 16,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,83; 14,4</t>
+          <t>12,67; 14,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,18; 15,04</t>
+          <t>12,09; 15,17</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>76928; 111165</t>
+          <t>75951; 112066</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89517; 130676</t>
+          <t>91824; 130761</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35786; 63236</t>
+          <t>36498; 65019</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62381; 93541</t>
+          <t>64538; 94919</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>72881; 107692</t>
+          <t>71436; 107033</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>105109; 149384</t>
+          <t>106729; 149603</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48416; 79970</t>
+          <t>48651; 80325</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57527; 82715</t>
+          <t>58290; 82092</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>156931; 207312</t>
+          <t>156364; 208801</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>205853; 263920</t>
+          <t>208697; 268024</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92694; 133986</t>
+          <t>91653; 133675</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>129088; 168087</t>
+          <t>128248; 168280</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>288578; 353554</t>
+          <t>288815; 353665</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>350895; 422342</t>
+          <t>348782; 420695</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>284670; 358126</t>
+          <t>284002; 355385</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>259910; 428914</t>
+          <t>258093; 427721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>216055; 274002</t>
+          <t>213227; 270300</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>246891; 310948</t>
+          <t>247059; 309650</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>282961; 348839</t>
+          <t>282702; 346519</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>207381; 339181</t>
+          <t>209907; 339769</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>519328; 602998</t>
+          <t>517212; 606109</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>614769; 710319</t>
+          <t>614010; 707542</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>589580; 680466</t>
+          <t>589183; 680347</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>515852; 742708</t>
+          <t>529298; 744787</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>81031; 118314</t>
+          <t>82223; 119051</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>88384; 125024</t>
+          <t>87865; 123623</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66683; 105017</t>
+          <t>68052; 104015</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73694; 110747</t>
+          <t>72343; 109583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>71437; 105462</t>
+          <t>73779; 108491</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54871; 86831</t>
+          <t>54819; 87731</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80269; 117779</t>
+          <t>80249; 116969</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>74000; 109096</t>
+          <t>75312; 108641</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>165005; 216973</t>
+          <t>164580; 212663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>149991; 200780</t>
+          <t>151710; 203051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>157960; 210572</t>
+          <t>161519; 211068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>155510; 205863</t>
+          <t>156263; 208473</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>470835; 553488</t>
+          <t>471293; 558570</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>554891; 645801</t>
+          <t>554770; 642474</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>414105; 494647</t>
+          <t>415727; 497857</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>420411; 594206</t>
+          <t>411113; 593205</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>380482; 456084</t>
+          <t>384174; 457603</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>432906; 517701</t>
+          <t>427052; 512158</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>434059; 516821</t>
+          <t>433287; 513680</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>369431; 495681</t>
+          <t>368219; 498914</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>873613; 990516</t>
+          <t>873195; 991115</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1019911; 1140073</t>
+          <t>1007952; 1133797</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>879125; 987222</t>
+          <t>868504; 985985</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>864370; 1067165</t>
+          <t>857548; 1076679</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P45C_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 10,9</t>
+          <t>7,3; 10,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 13,53</t>
+          <t>9,42; 13,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 8,71</t>
+          <t>5,02; 8,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,56; 18,47</t>
+          <t>11,4; 17,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 8,15</t>
+          <t>5,5; 8,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,07; 11,32</t>
+          <t>8,05; 11,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,15</t>
+          <t>4,94; 8,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,72; 10,87</t>
+          <t>7,78; 10,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 8,92</t>
+          <t>6,71; 8,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,12; 11,71</t>
+          <t>9,11; 11,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 7,72</t>
+          <t>5,37; 7,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,11; 13,26</t>
+          <t>9,81; 12,81</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,09; 20,93</t>
+          <t>17,33; 21,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,88; 21,57</t>
+          <t>18,0; 21,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,78; 17,24</t>
+          <t>13,98; 17,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,3; 18,73</t>
+          <t>16,31; 20,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,47; 17,08</t>
+          <t>13,63; 17,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,18; 17,78</t>
+          <t>14,24; 17,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,29; 17,52</t>
+          <t>14,36; 17,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 15,2</t>
+          <t>13,32; 16,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,8; 18,52</t>
+          <t>15,78; 18,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,63; 19,16</t>
+          <t>16,73; 19,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,59; 16,85</t>
+          <t>14,53; 17,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,71; 16,48</t>
+          <t>15,28; 17,89</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,93; 21,62</t>
+          <t>15,33; 22,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,49; 26,01</t>
+          <t>18,35; 26,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,57; 19,22</t>
+          <t>12,76; 19,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,19; 16,95</t>
+          <t>12,2; 18,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,52; 22,82</t>
+          <t>15,61; 22,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,03; 19,25</t>
+          <t>12,33; 19,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,78; 21,55</t>
+          <t>14,62; 21,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,4; 16,45</t>
+          <t>11,49; 16,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,04; 20,73</t>
+          <t>16,13; 21,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,3; 21,81</t>
+          <t>16,25; 21,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,9; 19,47</t>
+          <t>14,62; 19,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,96; 15,95</t>
+          <t>12,56; 16,34</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,42; 17,09</t>
+          <t>14,45; 17,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,36; 18,94</t>
+          <t>16,14; 18,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,42; 14,87</t>
+          <t>12,31; 14,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 17,22</t>
+          <t>15,6; 18,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,4; 13,57</t>
+          <t>11,29; 13,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,13; 14,55</t>
+          <t>12,24; 14,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,36; 14,65</t>
+          <t>12,29; 14,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,09; 13,66</t>
+          <t>12,39; 14,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,15; 14,93</t>
+          <t>13,26; 14,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,58; 16,4</t>
+          <t>14,65; 16,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,67; 14,38</t>
+          <t>12,68; 14,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 15,17</t>
+          <t>14,18; 16,05</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77197</t>
+          <t>83198</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69357</t>
+          <t>74760</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>146554</t>
+          <t>157959</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75951; 112066</t>
+          <t>75084; 112583</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91824; 130761</t>
+          <t>90986; 130968</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36498; 65019</t>
+          <t>37464; 65107</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64538; 94919</t>
+          <t>65862; 100184</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71436; 107033</t>
+          <t>72210; 106801</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>106729; 149603</t>
+          <t>106362; 149586</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48651; 80325</t>
+          <t>48663; 78886</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58290; 82092</t>
+          <t>63903; 88839</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>156364; 208801</t>
+          <t>157021; 210182</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>208697; 268024</t>
+          <t>208568; 265008</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>91653; 133675</t>
+          <t>92893; 135970</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>128248; 168280</t>
+          <t>137211; 179155</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364936</t>
+          <t>408330</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>290402</t>
+          <t>320440</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>655339</t>
+          <t>728770</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>288815; 353665</t>
+          <t>292783; 355114</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>348782; 420695</t>
+          <t>350987; 421394</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>284002; 355385</t>
+          <t>288089; 351806</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>258093; 427721</t>
+          <t>362742; 454651</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>213227; 270300</t>
+          <t>215733; 271340</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>247059; 309650</t>
+          <t>247980; 308545</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>282702; 346519</t>
+          <t>283972; 351031</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>209907; 339769</t>
+          <t>288766; 353835</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>517212; 606109</t>
+          <t>516397; 608321</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>614010; 707542</t>
+          <t>617533; 708220</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>589183; 680347</t>
+          <t>586730; 687536</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>529298; 744787</t>
+          <t>670940; 785712</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89884</t>
+          <t>106671</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90266</t>
+          <t>101720</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>180150</t>
+          <t>208391</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82223; 119051</t>
+          <t>84395; 123149</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87865; 123623</t>
+          <t>87197; 127099</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68052; 104015</t>
+          <t>69039; 104534</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72343; 109583</t>
+          <t>86815; 131281</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>73779; 108491</t>
+          <t>74210; 106605</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54819; 87731</t>
+          <t>56181; 86770</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80249; 116969</t>
+          <t>79379; 115988</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75312; 108641</t>
+          <t>84454; 119624</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164580; 212663</t>
+          <t>165478; 216768</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>151710; 203051</t>
+          <t>151265; 202473</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>161519; 211068</t>
+          <t>158483; 208653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>156263; 208473</t>
+          <t>181676; 236371</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>532017</t>
+          <t>598199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>450026</t>
+          <t>496921</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>982043</t>
+          <t>1095120</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>471293; 558570</t>
+          <t>472239; 557285</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>554770; 642474</t>
+          <t>547354; 641957</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>415727; 497857</t>
+          <t>412280; 495710</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>411113; 593205</t>
+          <t>548029; 654372</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>384174; 457603</t>
+          <t>380718; 459893</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>427052; 512158</t>
+          <t>430685; 514693</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>433287; 513680</t>
+          <t>430801; 515419</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>368219; 498914</t>
+          <t>461310; 538169</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>873195; 991115</t>
+          <t>880119; 988972</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1007952; 1133797</t>
+          <t>1012670; 1135267</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>868504; 985985</t>
+          <t>868824; 983008</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>857548; 1076679</t>
+          <t>1026550; 1161673</t>
         </is>
       </c>
     </row>
